--- a/data/vendors-template.xlsx
+++ b/data/vendors-template.xlsx
@@ -12,7 +12,7 @@
     <sheet name="Pružatelji" sheetId="3" r:id="rId3"/>
     <sheet name="Recenzije" sheetId="4" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="144525"/>
 </workbook>
 </file>
 
@@ -359,7 +359,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="264" uniqueCount="164">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="356" uniqueCount="200">
   <si>
     <t>WEDIPLAN — predložak za unos pružatelja</t>
   </si>
@@ -851,13 +851,121 @@
   </si>
   <si>
     <t>45.554711004652255, 18.695779367539384</t>
+  </si>
+  <si>
+    <t>45.551380188878355, 18.718577623695705</t>
+  </si>
+  <si>
+    <t>Studio Simba</t>
+  </si>
+  <si>
+    <t>https://simba.com.hr/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">photographysimba@gmail.com </t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/studio.simba/</t>
+  </si>
+  <si>
+    <t>info@studioc.hr</t>
+  </si>
+  <si>
+    <t>091 253 93 53</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/fotostudioc/</t>
+  </si>
+  <si>
+    <t>Studio C</t>
+  </si>
+  <si>
+    <t>https://www.studioc.hr/</t>
+  </si>
+  <si>
+    <t>Classic Cars for Rent Split Croatia</t>
+  </si>
+  <si>
+    <t>43.51459542665039, 16.45184871258262</t>
+  </si>
+  <si>
+    <t>Catering Kvatrić</t>
+  </si>
+  <si>
+    <t>https://catering-kvatric.hr/vjencanja/</t>
+  </si>
+  <si>
+    <t>45.82191026154278, 16.024483982000998</t>
+  </si>
+  <si>
+    <t>Zvona Catering</t>
+  </si>
+  <si>
+    <t>zvonacatering.hr</t>
+  </si>
+  <si>
+    <t>45.79494581931543, 15.928551068506366</t>
+  </si>
+  <si>
+    <t>Seven Wedding &amp; Events / Catering Split</t>
+  </si>
+  <si>
+    <t>https://www.salazavjencanja.com/catering-split-seven-wedding-events/</t>
+  </si>
+  <si>
+    <t>43.55070395768302, 16.42931474326798</t>
+  </si>
+  <si>
+    <t>45.81355897369877, 15.982214314044352</t>
+  </si>
+  <si>
+    <t>Vintage Empire Zagreb</t>
+  </si>
+  <si>
+    <t>Grupa Prvi Plan</t>
+  </si>
+  <si>
+    <t>Zadar</t>
+  </si>
+  <si>
+    <t>M2 Band Novska</t>
+  </si>
+  <si>
+    <t>Novska</t>
+  </si>
+  <si>
+    <t>Click Band</t>
+  </si>
+  <si>
+    <t>Grupa Status Zagreb</t>
+  </si>
+  <si>
+    <t>Showtime Band Vinkovci</t>
+  </si>
+  <si>
+    <t>Vinkovci</t>
+  </si>
+  <si>
+    <t>44.11904198700834, 15.230044684671324</t>
+  </si>
+  <si>
+    <t>45.33936602408229, 16.979213718988955</t>
+  </si>
+  <si>
+    <t>45.288048367359096, 18.806884700099072</t>
+  </si>
+  <si>
+    <t>43.51476954211381, 16.44449541179862</t>
+  </si>
+  <si>
+    <t>1250-2450 €</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -900,6 +1008,14 @@
       <sz val="11"/>
       <name val="Carlito"/>
     </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -937,11 +1053,12 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -959,17 +1076,13 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="2"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="2" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="3">
+    <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="1"/>
   </cellStyles>
@@ -1542,7 +1655,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:U37"/>
+  <dimension ref="A1:U40"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="25.42578125" bestFit="1" customWidth="1"/>
@@ -1777,11 +1890,11 @@
         <v>1</v>
       </c>
       <c r="H4">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="5" spans="1:21" ht="29.25">
-      <c r="A5" s="7" t="s">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="5" spans="1:21">
+      <c r="A5" t="s">
         <v>104</v>
       </c>
       <c r="B5" t="s">
@@ -1790,10 +1903,10 @@
       <c r="C5" t="s">
         <v>15</v>
       </c>
-      <c r="D5" s="8" t="s">
+      <c r="D5" t="s">
         <v>126</v>
       </c>
-      <c r="E5" s="9" t="s">
+      <c r="E5" t="s">
         <v>137</v>
       </c>
       <c r="F5" t="s">
@@ -1803,11 +1916,11 @@
         <v>1</v>
       </c>
       <c r="H5">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="6" spans="1:21" ht="29.25">
-      <c r="A6" s="7" t="s">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="6" spans="1:21">
+      <c r="A6" t="s">
         <v>105</v>
       </c>
       <c r="B6" t="s">
@@ -1816,10 +1929,10 @@
       <c r="C6" t="s">
         <v>15</v>
       </c>
-      <c r="D6" s="8" t="s">
+      <c r="D6" t="s">
         <v>127</v>
       </c>
-      <c r="E6" s="9" t="s">
+      <c r="E6" t="s">
         <v>138</v>
       </c>
       <c r="F6" t="s">
@@ -1829,11 +1942,11 @@
         <v>1</v>
       </c>
       <c r="H6">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="7" spans="1:21" ht="29.25">
-      <c r="A7" s="7" t="s">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="7" spans="1:21">
+      <c r="A7" t="s">
         <v>106</v>
       </c>
       <c r="B7" t="s">
@@ -1842,10 +1955,10 @@
       <c r="C7" t="s">
         <v>15</v>
       </c>
-      <c r="D7" s="8" t="s">
+      <c r="D7" t="s">
         <v>128</v>
       </c>
-      <c r="E7" s="9" t="s">
+      <c r="E7" t="s">
         <v>139</v>
       </c>
       <c r="F7" t="s">
@@ -1855,11 +1968,11 @@
         <v>1</v>
       </c>
       <c r="H7">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="8" spans="1:21" ht="29.25">
-      <c r="A8" s="7" t="s">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="8" spans="1:21">
+      <c r="A8" t="s">
         <v>107</v>
       </c>
       <c r="B8" t="s">
@@ -1868,10 +1981,10 @@
       <c r="C8" t="s">
         <v>18</v>
       </c>
-      <c r="D8" s="8" t="s">
+      <c r="D8" t="s">
         <v>129</v>
       </c>
-      <c r="E8" s="9" t="s">
+      <c r="E8" t="s">
         <v>140</v>
       </c>
       <c r="F8" t="s">
@@ -1881,11 +1994,11 @@
         <v>1</v>
       </c>
       <c r="H8">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="9" spans="1:21" ht="29.25">
-      <c r="A9" s="7" t="s">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="9" spans="1:21">
+      <c r="A9" t="s">
         <v>108</v>
       </c>
       <c r="B9" t="s">
@@ -1894,10 +2007,10 @@
       <c r="C9" t="s">
         <v>15</v>
       </c>
-      <c r="D9" s="8" t="s">
+      <c r="D9" t="s">
         <v>130</v>
       </c>
-      <c r="E9" s="9" t="s">
+      <c r="E9" t="s">
         <v>141</v>
       </c>
       <c r="F9" t="s">
@@ -1907,11 +2020,11 @@
         <v>1</v>
       </c>
       <c r="H9">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="10" spans="1:21" ht="57.75">
-      <c r="A10" s="7" t="s">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="10" spans="1:21">
+      <c r="A10" t="s">
         <v>109</v>
       </c>
       <c r="B10" t="s">
@@ -1920,10 +2033,10 @@
       <c r="C10" t="s">
         <v>15</v>
       </c>
-      <c r="D10" s="8" t="s">
+      <c r="D10" t="s">
         <v>131</v>
       </c>
-      <c r="E10" s="9" t="s">
+      <c r="E10" t="s">
         <v>158</v>
       </c>
       <c r="F10" t="s">
@@ -1933,11 +2046,11 @@
         <v>1</v>
       </c>
       <c r="H10">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="11" spans="1:21" ht="43.5">
-      <c r="A11" s="7" t="s">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="11" spans="1:21">
+      <c r="A11" t="s">
         <v>110</v>
       </c>
       <c r="B11" t="s">
@@ -1946,10 +2059,10 @@
       <c r="C11" t="s">
         <v>27</v>
       </c>
-      <c r="D11" s="8" t="s">
+      <c r="D11" t="s">
         <v>132</v>
       </c>
-      <c r="E11" s="9" t="s">
+      <c r="E11" t="s">
         <v>157</v>
       </c>
       <c r="F11" t="s">
@@ -1959,11 +2072,11 @@
         <v>1</v>
       </c>
       <c r="H11">
-        <v>1000</v>
+        <v>500</v>
       </c>
     </row>
     <row r="12" spans="1:21">
-      <c r="A12" s="7" t="s">
+      <c r="A12" t="s">
         <v>111</v>
       </c>
       <c r="B12" t="s">
@@ -1972,10 +2085,10 @@
       <c r="C12" t="s">
         <v>27</v>
       </c>
-      <c r="D12" s="8" t="s">
+      <c r="D12" t="s">
         <v>132</v>
       </c>
-      <c r="E12" s="9" t="s">
+      <c r="E12" t="s">
         <v>142</v>
       </c>
       <c r="F12" t="s">
@@ -1985,11 +2098,11 @@
         <v>1</v>
       </c>
       <c r="H12">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="13" spans="1:21" ht="29.25">
-      <c r="A13" s="7" t="s">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="13" spans="1:21">
+      <c r="A13" t="s">
         <v>112</v>
       </c>
       <c r="B13" t="s">
@@ -1998,10 +2111,10 @@
       <c r="C13" t="s">
         <v>27</v>
       </c>
-      <c r="D13" s="8" t="s">
+      <c r="D13" t="s">
         <v>132</v>
       </c>
-      <c r="E13" s="9" t="s">
+      <c r="E13" t="s">
         <v>143</v>
       </c>
       <c r="F13" t="s">
@@ -2011,11 +2124,11 @@
         <v>1</v>
       </c>
       <c r="H13">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="14" spans="1:21" ht="29.25">
-      <c r="A14" s="7" t="s">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="14" spans="1:21">
+      <c r="A14" t="s">
         <v>113</v>
       </c>
       <c r="B14" t="s">
@@ -2024,10 +2137,10 @@
       <c r="C14" t="s">
         <v>21</v>
       </c>
-      <c r="D14" s="8" t="s">
+      <c r="D14" t="s">
         <v>133</v>
       </c>
-      <c r="E14" s="9" t="s">
+      <c r="E14" t="s">
         <v>144</v>
       </c>
       <c r="F14" t="s">
@@ -2037,11 +2150,11 @@
         <v>1</v>
       </c>
       <c r="H14">
-        <v>1000</v>
+        <v>500</v>
       </c>
     </row>
     <row r="15" spans="1:21" ht="36" customHeight="1">
-      <c r="A15" s="7" t="s">
+      <c r="A15" t="s">
         <v>114</v>
       </c>
       <c r="B15" t="s">
@@ -2050,10 +2163,10 @@
       <c r="C15" t="s">
         <v>21</v>
       </c>
-      <c r="D15" s="8" t="s">
+      <c r="D15" t="s">
         <v>133</v>
       </c>
-      <c r="E15" s="9" t="s">
+      <c r="E15" t="s">
         <v>145</v>
       </c>
       <c r="F15" t="s">
@@ -2063,11 +2176,11 @@
         <v>1</v>
       </c>
       <c r="H15">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="16" spans="1:21" ht="29.25">
-      <c r="A16" s="7" t="s">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="16" spans="1:21">
+      <c r="A16" t="s">
         <v>115</v>
       </c>
       <c r="B16" t="s">
@@ -2076,10 +2189,10 @@
       <c r="C16" t="s">
         <v>21</v>
       </c>
-      <c r="D16" s="8" t="s">
+      <c r="D16" t="s">
         <v>133</v>
       </c>
-      <c r="E16" s="9" t="s">
+      <c r="E16" t="s">
         <v>146</v>
       </c>
       <c r="F16" t="s">
@@ -2089,11 +2202,11 @@
         <v>1</v>
       </c>
       <c r="H16">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" ht="29.25">
-      <c r="A17" s="7" t="s">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="17" spans="1:21">
+      <c r="A17" t="s">
         <v>116</v>
       </c>
       <c r="B17" t="s">
@@ -2102,10 +2215,10 @@
       <c r="C17" t="s">
         <v>21</v>
       </c>
-      <c r="D17" s="8" t="s">
+      <c r="D17" t="s">
         <v>133</v>
       </c>
-      <c r="E17" s="9" t="s">
+      <c r="E17" t="s">
         <v>147</v>
       </c>
       <c r="F17" t="s">
@@ -2115,11 +2228,11 @@
         <v>1</v>
       </c>
       <c r="H17">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" ht="29.25">
-      <c r="A18" s="7" t="s">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="18" spans="1:21">
+      <c r="A18" t="s">
         <v>117</v>
       </c>
       <c r="B18" t="s">
@@ -2128,10 +2241,10 @@
       <c r="C18" t="s">
         <v>24</v>
       </c>
-      <c r="D18" s="8" t="s">
+      <c r="D18" t="s">
         <v>134</v>
       </c>
-      <c r="E18" s="9" t="s">
+      <c r="E18" t="s">
         <v>148</v>
       </c>
       <c r="F18" t="s">
@@ -2141,11 +2254,11 @@
         <v>1</v>
       </c>
       <c r="H18">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" ht="29.25">
-      <c r="A19" s="7" t="s">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="19" spans="1:21">
+      <c r="A19" t="s">
         <v>118</v>
       </c>
       <c r="B19" t="s">
@@ -2154,10 +2267,10 @@
       <c r="C19" t="s">
         <v>24</v>
       </c>
-      <c r="D19" s="8" t="s">
+      <c r="D19" t="s">
         <v>134</v>
       </c>
-      <c r="E19" s="9" t="s">
+      <c r="E19" t="s">
         <v>149</v>
       </c>
       <c r="F19" t="s">
@@ -2167,11 +2280,11 @@
         <v>1</v>
       </c>
       <c r="H19">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" ht="57.75">
-      <c r="A20" s="7" t="s">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="20" spans="1:21">
+      <c r="A20" t="s">
         <v>119</v>
       </c>
       <c r="B20" t="s">
@@ -2180,10 +2293,10 @@
       <c r="C20" t="s">
         <v>24</v>
       </c>
-      <c r="D20" s="8" t="s">
+      <c r="D20" t="s">
         <v>135</v>
       </c>
-      <c r="E20" s="9" t="s">
+      <c r="E20" t="s">
         <v>156</v>
       </c>
       <c r="F20" t="s">
@@ -2193,11 +2306,11 @@
         <v>1</v>
       </c>
       <c r="H20">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" ht="29.25">
-      <c r="A21" s="7" t="s">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="21" spans="1:21">
+      <c r="A21" t="s">
         <v>120</v>
       </c>
       <c r="B21" t="s">
@@ -2206,10 +2319,10 @@
       <c r="C21" t="s">
         <v>24</v>
       </c>
-      <c r="D21" s="8" t="s">
+      <c r="D21" t="s">
         <v>134</v>
       </c>
-      <c r="E21" s="9" t="s">
+      <c r="E21" t="s">
         <v>150</v>
       </c>
       <c r="F21" t="s">
@@ -2219,11 +2332,11 @@
         <v>1</v>
       </c>
       <c r="H21">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" ht="29.25">
-      <c r="A22" s="7" t="s">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="22" spans="1:21">
+      <c r="A22" t="s">
         <v>121</v>
       </c>
       <c r="B22" t="s">
@@ -2232,10 +2345,10 @@
       <c r="C22" t="s">
         <v>24</v>
       </c>
-      <c r="D22" s="8" t="s">
+      <c r="D22" t="s">
         <v>134</v>
       </c>
-      <c r="E22" s="9" t="s">
+      <c r="E22" t="s">
         <v>155</v>
       </c>
       <c r="F22" t="s">
@@ -2245,11 +2358,11 @@
         <v>1</v>
       </c>
       <c r="H22">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" ht="43.5">
-      <c r="A23" s="7" t="s">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="23" spans="1:21">
+      <c r="A23" t="s">
         <v>122</v>
       </c>
       <c r="B23" t="s">
@@ -2258,10 +2371,10 @@
       <c r="C23" t="s">
         <v>21</v>
       </c>
-      <c r="D23" s="8" t="s">
+      <c r="D23" t="s">
         <v>74</v>
       </c>
-      <c r="E23" s="9" t="s">
+      <c r="E23" t="s">
         <v>154</v>
       </c>
       <c r="F23" t="s">
@@ -2271,11 +2384,11 @@
         <v>1</v>
       </c>
       <c r="H23">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" ht="29.25">
-      <c r="A24" s="7" t="s">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="24" spans="1:21">
+      <c r="A24" t="s">
         <v>123</v>
       </c>
       <c r="B24" t="s">
@@ -2284,10 +2397,10 @@
       <c r="C24" t="s">
         <v>21</v>
       </c>
-      <c r="D24" s="8" t="s">
+      <c r="D24" t="s">
         <v>136</v>
       </c>
-      <c r="E24" s="9" t="s">
+      <c r="E24" t="s">
         <v>151</v>
       </c>
       <c r="F24" t="s">
@@ -2297,11 +2410,11 @@
         <v>1</v>
       </c>
       <c r="H24">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" ht="29.25">
-      <c r="A25" s="7" t="s">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="25" spans="1:21">
+      <c r="A25" t="s">
         <v>124</v>
       </c>
       <c r="B25" t="s">
@@ -2310,10 +2423,10 @@
       <c r="C25" t="s">
         <v>21</v>
       </c>
-      <c r="D25" s="8" t="s">
+      <c r="D25" t="s">
         <v>74</v>
       </c>
-      <c r="E25" s="9" t="s">
+      <c r="E25" t="s">
         <v>152</v>
       </c>
       <c r="F25" t="s">
@@ -2323,20 +2436,20 @@
         <v>1</v>
       </c>
       <c r="H25">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8" ht="29.25">
-      <c r="A26" s="9" t="s">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="26" spans="1:21">
+      <c r="A26" t="s">
         <v>125</v>
       </c>
       <c r="B26" t="s">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="C26" t="s">
         <v>21</v>
       </c>
-      <c r="D26" s="8" t="s">
+      <c r="D26" t="s">
         <v>74</v>
       </c>
       <c r="E26" t="s">
@@ -2346,155 +2459,430 @@
         <v>76</v>
       </c>
       <c r="G26">
-        <v>1</v>
+        <v>40</v>
       </c>
       <c r="H26">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8">
-      <c r="A27" s="9" t="s">
+        <v>100</v>
+      </c>
+      <c r="I26">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="J26">
+        <v>132</v>
+      </c>
+      <c r="K26" t="s">
+        <v>77</v>
+      </c>
+      <c r="L26" t="s">
+        <v>78</v>
+      </c>
+      <c r="M26" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="27" spans="1:21">
+      <c r="A27" t="s">
         <v>159</v>
       </c>
       <c r="B27" t="s">
         <v>31</v>
       </c>
-      <c r="C27" s="9" t="s">
+      <c r="C27" t="s">
         <v>24</v>
       </c>
-      <c r="D27" s="9" t="s">
+      <c r="D27" t="s">
         <v>160</v>
       </c>
       <c r="E27" t="s">
         <v>162</v>
       </c>
-      <c r="F27" s="9" t="s">
+      <c r="F27" t="s">
         <v>89</v>
       </c>
       <c r="G27">
-        <v>1000</v>
-      </c>
-      <c r="H27">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="28" spans="1:8">
-      <c r="A28" s="9" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:21">
+      <c r="A28" t="s">
         <v>161</v>
       </c>
       <c r="B28" t="s">
         <v>29</v>
       </c>
-      <c r="C28" s="9" t="s">
+      <c r="C28" t="s">
         <v>27</v>
       </c>
-      <c r="D28" s="9" t="s">
+      <c r="D28" t="s">
         <v>132</v>
       </c>
       <c r="E28" t="s">
         <v>163</v>
       </c>
-      <c r="F28" s="9" t="s">
+      <c r="F28" t="s">
         <v>89</v>
       </c>
       <c r="G28">
-        <v>1000</v>
-      </c>
-      <c r="H28">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="29" spans="1:8">
-      <c r="A29" s="9"/>
-      <c r="C29" s="9"/>
-      <c r="D29" s="9"/>
-      <c r="F29" s="9"/>
-      <c r="G29" s="9"/>
-      <c r="H29" s="9"/>
-    </row>
-    <row r="30" spans="1:8">
-      <c r="A30" s="9"/>
-      <c r="C30" s="9"/>
-      <c r="D30" s="9"/>
-      <c r="E30" s="9"/>
-      <c r="F30" s="9"/>
-      <c r="G30" s="9"/>
-      <c r="H30" s="9"/>
-    </row>
-    <row r="31" spans="1:8">
-      <c r="A31" s="9"/>
-      <c r="C31" s="9"/>
-      <c r="D31" s="9"/>
-      <c r="E31" s="9"/>
-      <c r="F31" s="9"/>
-      <c r="G31" s="9"/>
-      <c r="H31" s="9"/>
-    </row>
-    <row r="32" spans="1:8">
-      <c r="A32" s="9"/>
-      <c r="C32" s="9"/>
-      <c r="D32" s="9"/>
-      <c r="E32" s="9"/>
-      <c r="F32" s="9"/>
-      <c r="G32" s="9"/>
-      <c r="H32" s="9"/>
-    </row>
-    <row r="33" spans="1:8">
-      <c r="A33" s="9"/>
-      <c r="C33" s="9"/>
-      <c r="D33" s="9"/>
-      <c r="E33" s="9"/>
-      <c r="F33" s="9"/>
-      <c r="G33" s="9"/>
-      <c r="H33" s="9"/>
-    </row>
-    <row r="34" spans="1:8">
-      <c r="A34" s="9"/>
-      <c r="C34" s="9"/>
-      <c r="D34" s="9"/>
-      <c r="E34" s="9"/>
-      <c r="F34" s="9"/>
-      <c r="G34" s="9"/>
-      <c r="H34" s="9"/>
-    </row>
-    <row r="35" spans="1:8">
-      <c r="A35" s="9"/>
-      <c r="C35" s="9"/>
-      <c r="D35" s="9"/>
-      <c r="E35" s="9"/>
-      <c r="F35" s="9"/>
-      <c r="G35" s="9"/>
-      <c r="H35" s="9"/>
-    </row>
-    <row r="36" spans="1:8">
-      <c r="A36" s="9"/>
-      <c r="C36" s="9"/>
-      <c r="D36" s="9"/>
-      <c r="E36" s="9"/>
-      <c r="F36" s="9"/>
-      <c r="G36" s="9"/>
-      <c r="H36" s="9"/>
-    </row>
-    <row r="37" spans="1:8">
-      <c r="A37" s="9"/>
-      <c r="C37" s="9"/>
-      <c r="D37" s="9"/>
-      <c r="E37" s="9"/>
-      <c r="F37" s="9"/>
-      <c r="G37" s="9"/>
-      <c r="H37" s="9"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:21">
+      <c r="A29" t="s">
+        <v>165</v>
+      </c>
+      <c r="B29" t="s">
+        <v>29</v>
+      </c>
+      <c r="C29" t="s">
+        <v>27</v>
+      </c>
+      <c r="D29" t="s">
+        <v>132</v>
+      </c>
+      <c r="E29" t="s">
+        <v>164</v>
+      </c>
+      <c r="F29" t="s">
+        <v>89</v>
+      </c>
+      <c r="G29">
+        <v>1250</v>
+      </c>
+      <c r="I29">
+        <v>5</v>
+      </c>
+      <c r="J29">
+        <v>42</v>
+      </c>
+      <c r="K29" t="s">
+        <v>77</v>
+      </c>
+      <c r="L29" t="s">
+        <v>78</v>
+      </c>
+      <c r="M29" t="s">
+        <v>79</v>
+      </c>
+      <c r="O29" t="s">
+        <v>199</v>
+      </c>
+      <c r="Q29" t="s">
+        <v>166</v>
+      </c>
+      <c r="S29" s="7" t="s">
+        <v>167</v>
+      </c>
+      <c r="U29" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="30" spans="1:21">
+      <c r="A30" t="s">
+        <v>172</v>
+      </c>
+      <c r="B30" t="s">
+        <v>29</v>
+      </c>
+      <c r="C30" t="s">
+        <v>27</v>
+      </c>
+      <c r="D30" t="s">
+        <v>132</v>
+      </c>
+      <c r="E30" t="s">
+        <v>163</v>
+      </c>
+      <c r="F30" t="s">
+        <v>89</v>
+      </c>
+      <c r="G30">
+        <v>1</v>
+      </c>
+      <c r="I30">
+        <v>4.8</v>
+      </c>
+      <c r="J30">
+        <v>259</v>
+      </c>
+      <c r="K30" t="s">
+        <v>77</v>
+      </c>
+      <c r="L30" t="s">
+        <v>78</v>
+      </c>
+      <c r="M30" t="s">
+        <v>79</v>
+      </c>
+      <c r="Q30" t="s">
+        <v>173</v>
+      </c>
+      <c r="R30" s="8" t="s">
+        <v>170</v>
+      </c>
+      <c r="S30" s="8" t="s">
+        <v>169</v>
+      </c>
+      <c r="U30" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="31" spans="1:21">
+      <c r="A31" t="s">
+        <v>174</v>
+      </c>
+      <c r="B31" t="s">
+        <v>42</v>
+      </c>
+      <c r="C31" t="s">
+        <v>21</v>
+      </c>
+      <c r="D31" t="s">
+        <v>74</v>
+      </c>
+      <c r="E31" t="s">
+        <v>175</v>
+      </c>
+      <c r="F31" t="s">
+        <v>89</v>
+      </c>
+      <c r="G31">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:21">
+      <c r="A32" t="s">
+        <v>176</v>
+      </c>
+      <c r="B32" t="s">
+        <v>26</v>
+      </c>
+      <c r="C32" t="s">
+        <v>24</v>
+      </c>
+      <c r="D32" t="s">
+        <v>134</v>
+      </c>
+      <c r="E32" t="s">
+        <v>178</v>
+      </c>
+      <c r="F32" t="s">
+        <v>89</v>
+      </c>
+      <c r="G32">
+        <v>1</v>
+      </c>
+      <c r="Q32" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="33" spans="1:17">
+      <c r="A33" t="s">
+        <v>179</v>
+      </c>
+      <c r="B33" t="s">
+        <v>26</v>
+      </c>
+      <c r="C33" t="s">
+        <v>24</v>
+      </c>
+      <c r="D33" t="s">
+        <v>134</v>
+      </c>
+      <c r="E33" t="s">
+        <v>181</v>
+      </c>
+      <c r="F33" t="s">
+        <v>89</v>
+      </c>
+      <c r="G33">
+        <v>1</v>
+      </c>
+      <c r="Q33" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="34" spans="1:17">
+      <c r="A34" t="s">
+        <v>182</v>
+      </c>
+      <c r="B34" t="s">
+        <v>26</v>
+      </c>
+      <c r="C34" t="s">
+        <v>21</v>
+      </c>
+      <c r="D34" t="s">
+        <v>74</v>
+      </c>
+      <c r="E34" t="s">
+        <v>184</v>
+      </c>
+      <c r="F34" t="s">
+        <v>89</v>
+      </c>
+      <c r="G34">
+        <v>1</v>
+      </c>
+      <c r="Q34" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="35" spans="1:17">
+      <c r="A35" t="s">
+        <v>186</v>
+      </c>
+      <c r="B35" t="s">
+        <v>42</v>
+      </c>
+      <c r="C35" t="s">
+        <v>24</v>
+      </c>
+      <c r="D35" t="s">
+        <v>134</v>
+      </c>
+      <c r="E35" t="s">
+        <v>185</v>
+      </c>
+      <c r="F35" t="s">
+        <v>89</v>
+      </c>
+      <c r="G35">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:17">
+      <c r="A36" t="s">
+        <v>187</v>
+      </c>
+      <c r="B36" t="s">
+        <v>31</v>
+      </c>
+      <c r="C36" t="s">
+        <v>21</v>
+      </c>
+      <c r="D36" t="s">
+        <v>188</v>
+      </c>
+      <c r="E36" t="s">
+        <v>195</v>
+      </c>
+      <c r="F36" t="s">
+        <v>89</v>
+      </c>
+      <c r="G36">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" spans="1:17">
+      <c r="A37" t="s">
+        <v>189</v>
+      </c>
+      <c r="B37" t="s">
+        <v>31</v>
+      </c>
+      <c r="C37" t="s">
+        <v>24</v>
+      </c>
+      <c r="D37" t="s">
+        <v>190</v>
+      </c>
+      <c r="E37" t="s">
+        <v>196</v>
+      </c>
+      <c r="F37" t="s">
+        <v>89</v>
+      </c>
+      <c r="G37">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" spans="1:17">
+      <c r="A38" t="s">
+        <v>191</v>
+      </c>
+      <c r="B38" t="s">
+        <v>31</v>
+      </c>
+      <c r="C38" t="s">
+        <v>21</v>
+      </c>
+      <c r="D38" t="s">
+        <v>74</v>
+      </c>
+      <c r="E38" t="s">
+        <v>198</v>
+      </c>
+      <c r="F38" t="s">
+        <v>89</v>
+      </c>
+      <c r="G38">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" spans="1:17">
+      <c r="A39" t="s">
+        <v>192</v>
+      </c>
+      <c r="B39" t="s">
+        <v>31</v>
+      </c>
+      <c r="C39" t="s">
+        <v>24</v>
+      </c>
+      <c r="D39" t="s">
+        <v>134</v>
+      </c>
+      <c r="E39" t="s">
+        <v>185</v>
+      </c>
+      <c r="F39" t="s">
+        <v>89</v>
+      </c>
+      <c r="G39">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:17">
+      <c r="A40" t="s">
+        <v>193</v>
+      </c>
+      <c r="B40" t="s">
+        <v>31</v>
+      </c>
+      <c r="C40" t="s">
+        <v>27</v>
+      </c>
+      <c r="D40" t="s">
+        <v>194</v>
+      </c>
+      <c r="E40" t="s">
+        <v>197</v>
+      </c>
+      <c r="F40" t="s">
+        <v>89</v>
+      </c>
+      <c r="G40">
+        <v>1</v>
+      </c>
     </row>
   </sheetData>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" sqref="F2:F498 D27">
+    <dataValidation type="list" allowBlank="1" sqref="D27 F2:F498">
       <formula1>"od (paušal),po osobi (raspon)"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" sqref="L2:M498">
       <formula1>"DA,NE"</formula1>
     </dataValidation>
   </dataValidations>
+  <hyperlinks>
+    <hyperlink ref="S29" r:id="rId1"/>
+    <hyperlink ref="S30" r:id="rId2" display="mailto:echoasoft1@gmail.com"/>
+    <hyperlink ref="R30" r:id="rId3" display="tel:+385912539353"/>
+    <hyperlink ref="Q32" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <legacyDrawing r:id="rId1"/>
+  <pageSetup orientation="portrait" r:id="rId5"/>
+  <legacyDrawing r:id="rId6"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="3">

--- a/data/vendors-template.xlsx
+++ b/data/vendors-template.xlsx
@@ -202,82 +202,97 @@
         <t>Odaberi iz padajućeg izbornika</t>
       </text>
     </comment>
+    <comment ref="D1" authorId="0" shapeId="0">
+      <text>
+        <t>SJEDIŠTE — jedan grad. Ako ih pružatelj navodi više, upiši glavni/prvi, ostale u pokrivanje_napomena. Prazno = poznata samo regija (bez pina na karti). OBAVEZNO za sale/konobe/kuće za proslavu.</t>
+      </text>
+    </comment>
     <comment ref="E1" authorId="0" shapeId="0">
       <text>
-        <t>Google Maps → desni klik na lokaciju → klik na koordinate (kopira "43.5081, 16.4402") → zalijepi ovdje</t>
+        <t>Google Maps → desni klik na lokaciju → klik na koordinate (kopira "43.5081, 16.4402") → zalijepi ovdje. Prazno = geokodira se iz grada (Faza 1). OBAVEZNO za sale/konobe/kuće za proslavu. Nikad ne izmišljaj koordinatu!</t>
       </text>
     </comment>
     <comment ref="F1" authorId="0" shapeId="0">
       <text>
+        <t>Gdje pružatelj RADI (uz svoju regiju). Više regija odvoji točka-zarezom: Dalmacija; Kvarner. Za cijelu državu upiši: cijela Hrvatska. Prazno = radi samo u svojoj regiji.</t>
+      </text>
+    </comment>
+    <comment ref="G1" authorId="0" shapeId="0">
+      <text>
+        <t>Slobodni tekst o pokrivanju, npr. 'radi u Splitu, Zadru i Šibeniku' ili 'po dogovoru i BiH'. Prikazuje se na profilu.</t>
+      </text>
+    </comment>
+    <comment ref="H1" authorId="0" shapeId="0">
+      <text>
         <t>od (paušal) = jedna cijena 'od X €'; po osobi (raspon) = X–Y €/os. (sale, catering)</t>
       </text>
     </comment>
-    <comment ref="G1" authorId="0" shapeId="0">
+    <comment ref="I1" authorId="0" shapeId="0">
       <text>
         <t>Samo broj u €, bez oznake valute</t>
       </text>
     </comment>
-    <comment ref="H1" authorId="0" shapeId="0">
+    <comment ref="J1" authorId="0" shapeId="0">
       <text>
         <t>Samo za 'po osobi (raspon)'</t>
       </text>
     </comment>
-    <comment ref="I1" authorId="0" shapeId="0">
+    <comment ref="K1" authorId="0" shapeId="0">
       <text>
         <t>0–5, npr. 4.8 — prenesena ocjena (Google i sl.). Ostavi prazno ako nema.</t>
       </text>
     </comment>
-    <comment ref="K1" authorId="0" shapeId="0">
+    <comment ref="M1" authorId="0" shapeId="0">
       <text>
         <t>OBAVEZNO ako je ocjena upisana, npr. 'Google recenzije'</t>
       </text>
     </comment>
-    <comment ref="L1" authorId="0" shapeId="0">
+    <comment ref="N1" authorId="0" shapeId="0">
       <text>
         <t>DA = kontaktirali smo ih i potvrdili podatke</t>
       </text>
     </comment>
-    <comment ref="M1" authorId="0" shapeId="0">
+    <comment ref="O1" authorId="0" shapeId="0">
       <text>
         <t>Zasad NE za sve — DA tek kad pružatelj dobije CRM</t>
       </text>
     </comment>
-    <comment ref="N1" authorId="0" shapeId="0">
+    <comment ref="P1" authorId="0" shapeId="0">
       <text>
         <t>Tagovi odvojeni zarezom, npr: uz more, terasa</t>
       </text>
     </comment>
-    <comment ref="O1" authorId="0" shapeId="0">
+    <comment ref="Q1" authorId="0" shapeId="0">
       <text>
         <t>Što pružatelj kaže o sebi (2–4 rečenice). Prazno = automatski tekst po kategoriji.</t>
       </text>
     </comment>
-    <comment ref="P1" authorId="0" shapeId="0">
+    <comment ref="R1" authorId="0" shapeId="0">
       <text>
         <t>Odvojeno zarezom. Prazno = automatski popis po kategoriji.</t>
       </text>
     </comment>
-    <comment ref="Q1" authorId="0" shapeId="0">
+    <comment ref="S1" authorId="0" shapeId="0">
       <text>
         <t>INTERNO — ne prikazuje se na stranici</t>
       </text>
     </comment>
-    <comment ref="R1" authorId="0" shapeId="0">
+    <comment ref="T1" authorId="0" shapeId="0">
       <text>
         <t>INTERNO — ne prikazuje se na stranici</t>
       </text>
     </comment>
-    <comment ref="S1" authorId="0" shapeId="0">
+    <comment ref="U1" authorId="0" shapeId="0">
       <text>
         <t>INTERNO — ne prikazuje se na stranici</t>
       </text>
     </comment>
-    <comment ref="T1" authorId="0" shapeId="0">
+    <comment ref="V1" authorId="0" shapeId="0">
       <text>
         <t>Za tvoje praćenje — ne utječe na import</t>
       </text>
     </comment>
-    <comment ref="U1" authorId="0" shapeId="0">
+    <comment ref="W1" authorId="0" shapeId="0">
       <text>
         <t>Interno</t>
       </text>
@@ -605,7 +620,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A17"/>
+  <dimension ref="A1:A25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" min="1" max="1"/>
@@ -643,76 +658,128 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>3. Prenesene recenzije (tekstualne) upisuj u list 'Recenzije' — poveži ih točnim nazivom pružatelja.</t>
-        </is>
-      </c>
+      <c r="A6" s="2" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>4. Kad želiš podatke na stranici, spremi ovu datoteku i pokreni:  npm run import:vendors -- putanja/do/datoteke.xlsx</t>
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>LOKACIJA I POKRIVANJE (sjedište ≠ područje rada):</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Skripta provjerava svaki redak (koordinate, kategorije, cijene…) i ispisuje greške s brojem retka.</t>
+          <t>• grad + koordinate = SJEDIŠTE (jedna točka → jedan pin na karti). pokriva_regije = gdje pružatelj RADI.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>5. Ako je sve u redu, generira data/vendors.json i data/profiles.json → git commit → podaci su na stranici.</t>
+          <t>• Nema grada? Ostavi grad i koordinate prazno — pružatelj se prikazuje u listi svoje regije, bez pina. NIKAD ne izmišljaj koordinatu.</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr"/>
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>• Više gradova (npr. Split, Zadar, Šibenik)? grad = glavni/prvi, ostali u pokrivanje_napomena. Jedan pružatelj = jedan pin.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>VAŽNO — DOZVOLE:</t>
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>• Više regija? pokriva_regije = 'Dalmacija; Kvarner'. Cijela država? pokriva_regije = 'cijela Hrvatska'.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>• Za objavu prenesenih recenzija, fotografija i ocjena zatraži suglasnost pružatelja (to je ujedno prvi kontakt za partnerstvo).</t>
+          <t>• IZNIMKA: Restorani i sale, Konobe i prostori, Najam kuće — grad i koordinate su OBAVEZNI (lokacija im je bit ponude).</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>• Kolone web/telefon/email su samo za tvoju evidenciju — import ih NE stavlja na stranicu (Direktan kontakt: zasad ne).</t>
+          <t>• Koordinate fotografa/bendova ne moraš tražiti ručno — dovoljan je grad, geokodiranje radi skripta (Faza 1). Vrijeme uloži u točne koordinate dvorana.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>• Redci čiji naziv počinje s 'PRIMJER' se preskaču pri importu — slobodno ih ostavi ili obriši.</t>
+          <t>3. Prenesene recenzije (tekstualne) upisuj u list 'Recenzije' — poveži ih točnim nazivom pružatelja.</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="inlineStr"/>
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>4. Kad želiš podatke na stranici, spremi ovu datoteku i pokreni:  npm run import:vendors -- putanja/do/datoteke.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>SAVJET ZA POČETAK:</t>
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Skripta provjerava svaki redak (koordinate, kategorije, cijene…) i ispisuje greške s brojem retka.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>5. Ako je sve u redu, generira data/vendors.json i data/profiles.json → git commit → podaci su na stranici.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>VAŽNO — DOZVOLE:</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>• Za objavu prenesenih recenzija, fotografija i ocjena zatraži suglasnost pružatelja (to je ujedno prvi kontakt za partnerstvo).</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>• Kolone web/telefon/email su samo za tvoju evidenciju — import ih NE stavlja na stranicu (Direktan kontakt: zasad ne).</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>• Redci čiji naziv počinje s 'PRIMJER' se preskaču pri importu — slobodno ih ostavi ili obriši.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t>SAVJET ZA POČETAK:</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
         <is>
           <t>• Kreni s 1 regijom i 2–3 kategorije (npr. Dalmacija: Restorani i sale + Foto i Video) da provjeriš cijeli tok, pa širi.</t>
         </is>
@@ -984,7 +1051,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U3"/>
+  <dimension ref="A1:W6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -992,22 +1059,24 @@
     <col width="16" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="20" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="11" customWidth="1" min="7" max="7"/>
-    <col width="11" customWidth="1" min="8" max="8"/>
-    <col width="9" customWidth="1" min="9" max="9"/>
-    <col width="13" customWidth="1" min="10" max="10"/>
-    <col width="16" customWidth="1" min="11" max="11"/>
-    <col width="12" customWidth="1" min="12" max="12"/>
-    <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="22" customWidth="1" min="14" max="14"/>
-    <col width="46" customWidth="1" min="15" max="15"/>
-    <col width="34" customWidth="1" min="16" max="16"/>
-    <col width="22" customWidth="1" min="17" max="17"/>
-    <col width="15" customWidth="1" min="18" max="18"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="26" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="11" customWidth="1" min="9" max="9"/>
+    <col width="11" customWidth="1" min="10" max="10"/>
+    <col width="9" customWidth="1" min="11" max="11"/>
+    <col width="13" customWidth="1" min="12" max="12"/>
+    <col width="16" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
+    <col width="14" customWidth="1" min="15" max="15"/>
+    <col width="22" customWidth="1" min="16" max="16"/>
+    <col width="46" customWidth="1" min="17" max="17"/>
+    <col width="34" customWidth="1" min="18" max="18"/>
     <col width="22" customWidth="1" min="19" max="19"/>
-    <col width="18" customWidth="1" min="20" max="20"/>
-    <col width="30" customWidth="1" min="21" max="21"/>
+    <col width="15" customWidth="1" min="20" max="20"/>
+    <col width="22" customWidth="1" min="21" max="21"/>
+    <col width="18" customWidth="1" min="22" max="22"/>
+    <col width="30" customWidth="1" min="23" max="23"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -1028,90 +1097,100 @@
       </c>
       <c r="D1" s="3" t="inlineStr">
         <is>
-          <t>grad*</t>
+          <t>grad</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
         <is>
-          <t>koordinate*</t>
+          <t>koordinate</t>
         </is>
       </c>
       <c r="F1" s="3" t="inlineStr">
         <is>
+          <t>pokriva_regije</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>pokrivanje_napomena</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="inlineStr">
+        <is>
           <t>nacin_cijene*</t>
         </is>
       </c>
-      <c r="G1" s="3" t="inlineStr">
+      <c r="I1" s="3" t="inlineStr">
         <is>
           <t>cijena_od*</t>
         </is>
       </c>
-      <c r="H1" s="3" t="inlineStr">
+      <c r="J1" s="3" t="inlineStr">
         <is>
           <t>cijena_do</t>
         </is>
       </c>
-      <c r="I1" s="3" t="inlineStr">
+      <c r="K1" s="3" t="inlineStr">
         <is>
           <t>ocjena</t>
         </is>
       </c>
-      <c r="J1" s="3" t="inlineStr">
+      <c r="L1" s="3" t="inlineStr">
         <is>
           <t>broj_recenzija</t>
         </is>
       </c>
-      <c r="K1" s="3" t="inlineStr">
+      <c r="M1" s="3" t="inlineStr">
         <is>
           <t>izvor_ocjene</t>
         </is>
       </c>
-      <c r="L1" s="3" t="inlineStr">
+      <c r="N1" s="3" t="inlineStr">
         <is>
           <t>provjereno</t>
         </is>
       </c>
-      <c r="M1" s="3" t="inlineStr">
+      <c r="O1" s="3" t="inlineStr">
         <is>
           <t>kalendar_uzivo</t>
         </is>
       </c>
-      <c r="N1" s="3" t="inlineStr">
+      <c r="P1" s="3" t="inlineStr">
         <is>
           <t>stil</t>
         </is>
       </c>
-      <c r="O1" s="3" t="inlineStr">
+      <c r="Q1" s="3" t="inlineStr">
         <is>
           <t>o_pruzatelju</t>
         </is>
       </c>
-      <c r="P1" s="3" t="inlineStr">
+      <c r="R1" s="3" t="inlineStr">
         <is>
           <t>usluge</t>
         </is>
       </c>
-      <c r="Q1" s="3" t="inlineStr">
+      <c r="S1" s="3" t="inlineStr">
         <is>
           <t>web</t>
         </is>
       </c>
-      <c r="R1" s="3" t="inlineStr">
+      <c r="T1" s="3" t="inlineStr">
         <is>
           <t>telefon</t>
         </is>
       </c>
-      <c r="S1" s="3" t="inlineStr">
+      <c r="U1" s="3" t="inlineStr">
         <is>
           <t>email</t>
         </is>
       </c>
-      <c r="T1" s="3" t="inlineStr">
+      <c r="V1" s="3" t="inlineStr">
         <is>
           <t>status</t>
         </is>
       </c>
-      <c r="U1" s="3" t="inlineStr">
+      <c r="W1" s="3" t="inlineStr">
         <is>
           <t>napomena</t>
         </is>
@@ -1143,74 +1222,76 @@
           <t>43.5147, 16.4102</t>
         </is>
       </c>
-      <c r="F2" s="4" t="inlineStr">
+      <c r="F2" s="4" t="inlineStr"/>
+      <c r="G2" s="4" t="inlineStr"/>
+      <c r="H2" s="4" t="inlineStr">
         <is>
           <t>po osobi (raspon)</t>
         </is>
       </c>
-      <c r="G2" s="4" t="n">
+      <c r="I2" s="4" t="n">
         <v>65</v>
       </c>
-      <c r="H2" s="4" t="n">
+      <c r="J2" s="4" t="n">
         <v>95</v>
       </c>
-      <c r="I2" s="4" t="n">
+      <c r="K2" s="4" t="n">
         <v>4.8</v>
       </c>
-      <c r="J2" s="4" t="n">
+      <c r="L2" s="4" t="n">
         <v>57</v>
       </c>
-      <c r="K2" s="4" t="inlineStr">
+      <c r="M2" s="4" t="inlineStr">
         <is>
           <t>Google recenzije</t>
         </is>
       </c>
-      <c r="L2" s="4" t="inlineStr">
+      <c r="N2" s="4" t="inlineStr">
         <is>
           <t>DA</t>
         </is>
       </c>
-      <c r="M2" s="4" t="inlineStr">
+      <c r="O2" s="4" t="inlineStr">
         <is>
           <t>NE</t>
         </is>
       </c>
-      <c r="N2" s="4" t="inlineStr">
+      <c r="P2" s="4" t="inlineStr">
         <is>
           <t>uz more, terasa</t>
         </is>
       </c>
-      <c r="O2" s="4" t="inlineStr">
+      <c r="Q2" s="4" t="inlineStr">
         <is>
           <t>Terasa uz more za do 220 gostiju, vlastita kuhinja i parking. Cijena po osobi uključuje meni od 5 slijedova.</t>
         </is>
       </c>
-      <c r="P2" s="4" t="inlineStr">
+      <c r="R2" s="4" t="inlineStr">
         <is>
           <t>Meni po osobi, Osoblje, Osnovna dekoracija, Parking</t>
         </is>
       </c>
-      <c r="Q2" s="4" t="inlineStr">
+      <c r="S2" s="4" t="inlineStr">
         <is>
           <t>villa-dalmacija.hr</t>
         </is>
       </c>
-      <c r="R2" s="4" t="inlineStr">
+      <c r="T2" s="4" t="inlineStr">
         <is>
           <t>021/555-123</t>
         </is>
       </c>
-      <c r="S2" s="4" t="inlineStr">
+      <c r="U2" s="4" t="inlineStr">
         <is>
           <t>info@villa-dalmacija.hr</t>
         </is>
       </c>
-      <c r="T2" s="4" t="inlineStr">
+      <c r="V2" s="4" t="inlineStr">
         <is>
           <t>Dozvola dobivena</t>
         </is>
       </c>
-      <c r="U2" s="4" t="inlineStr">
+      <c r="W2" s="4" t="inlineStr">
         <is>
           <t>primjer — obriši ili ostavi (preskače se)</t>
         </is>
@@ -1244,60 +1325,295 @@
       </c>
       <c r="F3" s="4" t="inlineStr">
         <is>
+          <t>Dalmacija; Kvarner</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>radi u Splitu, Zadru i Šibeniku, po dogovoru i šire</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
           <t>od (paušal)</t>
         </is>
       </c>
-      <c r="G3" s="4" t="n">
+      <c r="I3" s="4" t="n">
         <v>850</v>
       </c>
-      <c r="H3" s="4" t="n"/>
-      <c r="I3" s="4" t="n">
+      <c r="J3" s="4" t="n"/>
+      <c r="K3" s="4" t="n">
         <v>4.8</v>
       </c>
-      <c r="J3" s="4" t="n">
+      <c r="L3" s="4" t="n">
         <v>31</v>
       </c>
-      <c r="K3" s="4" t="inlineStr">
+      <c r="M3" s="4" t="inlineStr">
         <is>
           <t>Google recenzije</t>
         </is>
       </c>
-      <c r="L3" s="4" t="inlineStr">
+      <c r="N3" s="4" t="inlineStr">
         <is>
           <t>DA</t>
         </is>
       </c>
-      <c r="M3" s="4" t="inlineStr">
+      <c r="O3" s="4" t="inlineStr">
         <is>
           <t>NE</t>
         </is>
       </c>
-      <c r="N3" s="4" t="inlineStr">
+      <c r="P3" s="4" t="inlineStr">
         <is>
           <t>boho, film</t>
         </is>
       </c>
-      <c r="O3" s="4" t="inlineStr">
+      <c r="Q3" s="4" t="inlineStr">
         <is>
           <t>Vjenčanja fotografiramo od 2014. — reportažno, s naglaskom na svjetlo i emociju.</t>
         </is>
       </c>
-      <c r="P3" s="4" t="inlineStr"/>
-      <c r="Q3" s="4" t="inlineStr">
+      <c r="R3" s="4" t="inlineStr"/>
+      <c r="S3" s="4" t="inlineStr">
         <is>
           <t>fotostudio-anic.hr</t>
         </is>
       </c>
-      <c r="R3" s="4" t="inlineStr"/>
-      <c r="S3" s="4" t="inlineStr"/>
-      <c r="T3" s="4" t="inlineStr">
+      <c r="T3" s="4" t="inlineStr"/>
+      <c r="U3" s="4" t="inlineStr"/>
+      <c r="V3" s="4" t="inlineStr">
         <is>
           <t>Kontaktirano</t>
         </is>
       </c>
-      <c r="U3" s="4" t="inlineStr">
+      <c r="W3" s="4" t="inlineStr">
         <is>
           <t>primjer — preskače se pri importu</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>PRIMJER — Bend Adria</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>Glazba — bendovi</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>Dalmacija</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr"/>
+      <c r="E4" s="4" t="inlineStr"/>
+      <c r="F4" s="4" t="inlineStr"/>
+      <c r="G4" s="4" t="inlineStr"/>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>od (paušal)</t>
+        </is>
+      </c>
+      <c r="I4" s="4" t="n">
+        <v>1200</v>
+      </c>
+      <c r="J4" s="4" t="n"/>
+      <c r="K4" s="4" t="n"/>
+      <c r="L4" s="4" t="n"/>
+      <c r="M4" s="4" t="inlineStr"/>
+      <c r="N4" s="4" t="inlineStr">
+        <is>
+          <t>NE</t>
+        </is>
+      </c>
+      <c r="O4" s="4" t="inlineStr">
+        <is>
+          <t>NE</t>
+        </is>
+      </c>
+      <c r="P4" s="4" t="inlineStr">
+        <is>
+          <t>pop, rock</t>
+        </is>
+      </c>
+      <c r="Q4" s="4" t="inlineStr"/>
+      <c r="R4" s="4" t="inlineStr"/>
+      <c r="S4" s="4" t="inlineStr">
+        <is>
+          <t>bend-adria.hr</t>
+        </is>
+      </c>
+      <c r="T4" s="4" t="inlineStr"/>
+      <c r="U4" s="4" t="inlineStr"/>
+      <c r="V4" s="4" t="inlineStr">
+        <is>
+          <t>Istraženo</t>
+        </is>
+      </c>
+      <c r="W4" s="4" t="inlineStr">
+        <is>
+          <t>primjer — bez grada/koordinata → bez pina</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>PRIMJER — Ana Fotografija</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>Foto i Video</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>Istra</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>Pula</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr"/>
+      <c r="F5" s="4" t="inlineStr"/>
+      <c r="G5" s="4" t="inlineStr"/>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>na upit</t>
+        </is>
+      </c>
+      <c r="I5" s="4" t="n"/>
+      <c r="J5" s="4" t="n"/>
+      <c r="K5" s="4" t="n"/>
+      <c r="L5" s="4" t="n"/>
+      <c r="M5" s="4" t="inlineStr"/>
+      <c r="N5" s="4" t="inlineStr">
+        <is>
+          <t>NE</t>
+        </is>
+      </c>
+      <c r="O5" s="4" t="inlineStr">
+        <is>
+          <t>NE</t>
+        </is>
+      </c>
+      <c r="P5" s="4" t="inlineStr">
+        <is>
+          <t>elegantno</t>
+        </is>
+      </c>
+      <c r="Q5" s="4" t="inlineStr"/>
+      <c r="R5" s="4" t="inlineStr"/>
+      <c r="S5" s="4" t="inlineStr"/>
+      <c r="T5" s="4" t="inlineStr"/>
+      <c r="U5" s="4" t="inlineStr"/>
+      <c r="V5" s="4" t="inlineStr">
+        <is>
+          <t>Istraženo</t>
+        </is>
+      </c>
+      <c r="W5" s="4" t="inlineStr">
+        <is>
+          <t>primjer — koordinate se geokodiraju iz grada</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>PRIMJER — Perfect Day Weddings</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>Organizatori vjenčanja</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>Zagreb i okolica</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>Zagreb</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>45.8150, 15.9819</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>cijela Hrvatska</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>organiziramo vjenčanja u cijeloj Hrvatskoj</t>
+        </is>
+      </c>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>na upit</t>
+        </is>
+      </c>
+      <c r="I6" s="4" t="n"/>
+      <c r="J6" s="4" t="n"/>
+      <c r="K6" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="L6" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="M6" s="4" t="inlineStr">
+        <is>
+          <t>Google recenzije</t>
+        </is>
+      </c>
+      <c r="N6" s="4" t="inlineStr">
+        <is>
+          <t>DA</t>
+        </is>
+      </c>
+      <c r="O6" s="4" t="inlineStr">
+        <is>
+          <t>NE</t>
+        </is>
+      </c>
+      <c r="P6" s="4" t="inlineStr">
+        <is>
+          <t>full service</t>
+        </is>
+      </c>
+      <c r="Q6" s="4" t="inlineStr">
+        <is>
+          <t>Organiziramo vjenčanja od Istre do Slavonije — od koncepta do izvedbe.</t>
+        </is>
+      </c>
+      <c r="R6" s="4" t="inlineStr"/>
+      <c r="S6" s="4" t="inlineStr">
+        <is>
+          <t>perfectday.hr</t>
+        </is>
+      </c>
+      <c r="T6" s="4" t="inlineStr"/>
+      <c r="U6" s="4" t="inlineStr"/>
+      <c r="V6" s="4" t="inlineStr">
+        <is>
+          <t>Dozvola dobivena</t>
+        </is>
+      </c>
+      <c r="W6" s="4" t="inlineStr">
+        <is>
+          <t>primjer — pokriva cijelu HR</t>
         </is>
       </c>
     </row>
@@ -1309,16 +1625,16 @@
     <dataValidation sqref="C2:C500" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>Sifrarnici!$B$1:$B$5</formula1>
     </dataValidation>
-    <dataValidation sqref="F2:F500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="H2:H500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"od (paušal),po osobi (raspon)"</formula1>
     </dataValidation>
-    <dataValidation sqref="L2:L500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="N2:N500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"DA,NE"</formula1>
     </dataValidation>
-    <dataValidation sqref="M2:M500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="O2:O500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"DA,NE"</formula1>
     </dataValidation>
-    <dataValidation sqref="T2:T500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="V2:V500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>Sifrarnici!$C$1:$C$4</formula1>
     </dataValidation>
   </dataValidations>

--- a/data/vendors-template.xlsx
+++ b/data/vendors-template.xlsx
@@ -202,82 +202,107 @@
         <t>Odaberi iz padajućeg izbornika</t>
       </text>
     </comment>
+    <comment ref="D1" authorId="0" shapeId="0">
+      <text>
+        <t>SJEDIŠTE — jedan grad. Ako ih pružatelj navodi više, upiši glavni/prvi, ostale u pokrivanje_napomena. Prazno = poznata samo regija (bez pina na karti). OBAVEZNO za sale/konobe/kuće za proslavu.</t>
+      </text>
+    </comment>
     <comment ref="E1" authorId="0" shapeId="0">
       <text>
-        <t>Google Maps → desni klik na lokaciju → klik na koordinate (kopira "43.5081, 16.4402") → zalijepi ovdje</t>
+        <t>Google Maps → desni klik na lokaciju → klik na koordinate (kopira "43.5081, 16.4402") → zalijepi ovdje. Prazno = geokodira se iz grada (Faza 1). OBAVEZNO za sale/konobe/kuće za proslavu. Nikad ne izmišljaj koordinatu!</t>
       </text>
     </comment>
     <comment ref="F1" authorId="0" shapeId="0">
       <text>
+        <t>Gdje pružatelj RADI (uz svoju regiju). Više regija odvoji točka-zarezom: Dalmacija; Kvarner. Za cijelu državu upiši: cijela Hrvatska. Prazno = radi samo u svojoj regiji.</t>
+      </text>
+    </comment>
+    <comment ref="G1" authorId="0" shapeId="0">
+      <text>
+        <t>Slobodni tekst o pokrivanju, npr. 'radi u Splitu, Zadru i Šibeniku' ili 'po dogovoru i BiH'. Prikazuje se na profilu.</t>
+      </text>
+    </comment>
+    <comment ref="H1" authorId="0" shapeId="0">
+      <text>
         <t>od (paušal) = jedna cijena 'od X €'; po osobi (raspon) = X–Y €/os. (sale, catering)</t>
       </text>
     </comment>
-    <comment ref="G1" authorId="0" shapeId="0">
+    <comment ref="I1" authorId="0" shapeId="0">
       <text>
         <t>Samo broj u €, bez oznake valute</t>
       </text>
     </comment>
-    <comment ref="H1" authorId="0" shapeId="0">
+    <comment ref="J1" authorId="0" shapeId="0">
       <text>
         <t>Samo za 'po osobi (raspon)'</t>
       </text>
     </comment>
-    <comment ref="I1" authorId="0" shapeId="0">
+    <comment ref="K1" authorId="0" shapeId="0">
       <text>
         <t>0–5, npr. 4.8 — prenesena ocjena (Google i sl.). Ostavi prazno ako nema.</t>
       </text>
     </comment>
-    <comment ref="K1" authorId="0" shapeId="0">
+    <comment ref="M1" authorId="0" shapeId="0">
       <text>
         <t>OBAVEZNO ako je ocjena upisana, npr. 'Google recenzije'</t>
       </text>
     </comment>
-    <comment ref="L1" authorId="0" shapeId="0">
+    <comment ref="N1" authorId="0" shapeId="0">
       <text>
         <t>DA = kontaktirali smo ih i potvrdili podatke</t>
       </text>
     </comment>
-    <comment ref="M1" authorId="0" shapeId="0">
+    <comment ref="O1" authorId="0" shapeId="0">
       <text>
         <t>Zasad NE za sve — DA tek kad pružatelj dobije CRM</t>
       </text>
     </comment>
-    <comment ref="N1" authorId="0" shapeId="0">
+    <comment ref="P1" authorId="0" shapeId="0">
       <text>
         <t>Tagovi odvojeni zarezom, npr: uz more, terasa</t>
       </text>
     </comment>
-    <comment ref="O1" authorId="0" shapeId="0">
+    <comment ref="Q1" authorId="0" shapeId="0">
       <text>
         <t>Što pružatelj kaže o sebi (2–4 rečenice). Prazno = automatski tekst po kategoriji.</t>
       </text>
     </comment>
-    <comment ref="P1" authorId="0" shapeId="0">
+    <comment ref="R1" authorId="0" shapeId="0">
       <text>
         <t>Odvojeno zarezom. Prazno = automatski popis po kategoriji.</t>
       </text>
     </comment>
-    <comment ref="Q1" authorId="0" shapeId="0">
+    <comment ref="S1" authorId="0" shapeId="0">
+      <text>
+        <t>JAVNO — prikazuje se kao ikona na profilu. Zalijepi @handle, instagram.com/handle ili puni URL. Prazno = bez ikone.</t>
+      </text>
+    </comment>
+    <comment ref="T1" authorId="0" shapeId="0">
+      <text>
+        <t>JAVNO — prikazuje se kao ikona na profilu. Zalijepi facebook.com/stranica ili puni URL. Prazno = bez ikone.</t>
+      </text>
+    </comment>
+    <comment ref="U1" authorId="0" shapeId="0">
       <text>
         <t>INTERNO — ne prikazuje se na stranici</t>
       </text>
     </comment>
-    <comment ref="R1" authorId="0" shapeId="0">
+    <comment ref="V1" authorId="0" shapeId="0">
       <text>
         <t>INTERNO — ne prikazuje se na stranici</t>
       </text>
     </comment>
-    <comment ref="S1" authorId="0" shapeId="0">
+    <comment ref="W1" authorId="0" shapeId="0">
       <text>
         <t>INTERNO — ne prikazuje se na stranici</t>
       </text>
     </comment>
-    <comment ref="T1" authorId="0" shapeId="0">
+    <comment ref="X1" authorId="0" shapeId="0">
       <text>
         <t>Za tvoje praćenje — ne utječe na import</t>
       </text>
     </comment>
-    <comment ref="U1" authorId="0" shapeId="0">
+    <comment ref="Y1" authorId="0" shapeId="0">
       <text>
         <t>Interno</t>
       </text>
@@ -605,7 +630,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A17"/>
+  <dimension ref="A1:A26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" min="1" max="1"/>
@@ -643,76 +668,135 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>3. Prenesene recenzije (tekstualne) upisuj u list 'Recenzije' — poveži ih točnim nazivom pružatelja.</t>
-        </is>
-      </c>
+      <c r="A6" s="2" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>4. Kad želiš podatke na stranici, spremi ovu datoteku i pokreni:  npm run import:vendors -- putanja/do/datoteke.xlsx</t>
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>LOKACIJA I POKRIVANJE (sjedište ≠ područje rada):</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Skripta provjerava svaki redak (koordinate, kategorije, cijene…) i ispisuje greške s brojem retka.</t>
+          <t>• grad + koordinate = SJEDIŠTE (jedna točka → jedan pin na karti). pokriva_regije = gdje pružatelj RADI.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>5. Ako je sve u redu, generira data/vendors.json i data/profiles.json → git commit → podaci su na stranici.</t>
+          <t>• Nema grada? Ostavi grad i koordinate prazno — pružatelj se prikazuje u listi svoje regije, bez pina. NIKAD ne izmišljaj koordinatu.</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr"/>
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>• Više gradova (npr. Split, Zadar, Šibenik)? grad = glavni/prvi, ostali u pokrivanje_napomena. Jedan pružatelj = jedan pin.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>VAŽNO — DOZVOLE:</t>
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>• Više regija? pokriva_regije = 'Dalmacija; Kvarner'. Cijela država? pokriva_regije = 'cijela Hrvatska'.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>• Za objavu prenesenih recenzija, fotografija i ocjena zatraži suglasnost pružatelja (to je ujedno prvi kontakt za partnerstvo).</t>
+          <t>• IZNIMKA: Restorani i sale, Konobe i prostori, Najam kuće — grad i koordinate su OBAVEZNI (lokacija im je bit ponude).</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>• Kolone web/telefon/email su samo za tvoju evidenciju — import ih NE stavlja na stranicu (Direktan kontakt: zasad ne).</t>
+          <t>• Koordinate fotografa/bendova ne moraš tražiti ručno — dovoljan je grad, geokodiranje radi skripta (Faza 1). Vrijeme uloži u točne koordinate dvorana.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>• Redci čiji naziv počinje s 'PRIMJER' se preskaču pri importu — slobodno ih ostavi ili obriši.</t>
+          <t>3. Prenesene recenzije (tekstualne) upisuj u list 'Recenzije' — poveži ih točnim nazivom pružatelja.</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="inlineStr"/>
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>4. Kad želiš podatke na stranici, spremi ovu datoteku i pokreni:  npm run import:vendors -- putanja/do/datoteke.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>SAVJET ZA POČETAK:</t>
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Skripta provjerava svaki redak (koordinate, kategorije, cijene…) i ispisuje greške s brojem retka.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>5. Ako je sve u redu, generira data/vendors.json i data/profiles.json → git commit → podaci su na stranici.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>VAŽNO — DOZVOLE:</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>• Za objavu prenesenih recenzija, fotografija i ocjena zatraži suglasnost pružatelja (to je ujedno prvi kontakt za partnerstvo).</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>• Kolone web/telefon/email su samo za tvoju evidenciju — import ih NE stavlja na stranicu (Direktan kontakt: zasad ne).</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>• IZNIMKA: instagram i facebook SU javni — prikazuju se kao ikone na profilu pružatelja. Zalijepi @handle ili puni URL, ostalo sredi skripta.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>• Redci čiji naziv počinje s 'PRIMJER' se preskaču pri importu — slobodno ih ostavi ili obriši.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>SAVJET ZA POČETAK:</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
         <is>
           <t>• Kreni s 1 regijom i 2–3 kategorije (npr. Dalmacija: Restorani i sale + Foto i Video) da provjeriš cijeli tok, pa širi.</t>
         </is>
@@ -984,7 +1068,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U3"/>
+  <dimension ref="A1:Y6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -992,22 +1076,26 @@
     <col width="16" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="20" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="11" customWidth="1" min="7" max="7"/>
-    <col width="11" customWidth="1" min="8" max="8"/>
-    <col width="9" customWidth="1" min="9" max="9"/>
-    <col width="13" customWidth="1" min="10" max="10"/>
-    <col width="16" customWidth="1" min="11" max="11"/>
-    <col width="12" customWidth="1" min="12" max="12"/>
-    <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="22" customWidth="1" min="14" max="14"/>
-    <col width="46" customWidth="1" min="15" max="15"/>
-    <col width="34" customWidth="1" min="16" max="16"/>
-    <col width="22" customWidth="1" min="17" max="17"/>
-    <col width="15" customWidth="1" min="18" max="18"/>
-    <col width="22" customWidth="1" min="19" max="19"/>
-    <col width="18" customWidth="1" min="20" max="20"/>
-    <col width="30" customWidth="1" min="21" max="21"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="26" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="11" customWidth="1" min="9" max="9"/>
+    <col width="11" customWidth="1" min="10" max="10"/>
+    <col width="9" customWidth="1" min="11" max="11"/>
+    <col width="13" customWidth="1" min="12" max="12"/>
+    <col width="16" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
+    <col width="14" customWidth="1" min="15" max="15"/>
+    <col width="22" customWidth="1" min="16" max="16"/>
+    <col width="46" customWidth="1" min="17" max="17"/>
+    <col width="34" customWidth="1" min="18" max="18"/>
+    <col width="24" customWidth="1" min="19" max="19"/>
+    <col width="24" customWidth="1" min="20" max="20"/>
+    <col width="22" customWidth="1" min="21" max="21"/>
+    <col width="15" customWidth="1" min="22" max="22"/>
+    <col width="22" customWidth="1" min="23" max="23"/>
+    <col width="18" customWidth="1" min="24" max="24"/>
+    <col width="30" customWidth="1" min="25" max="25"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -1028,90 +1116,110 @@
       </c>
       <c r="D1" s="3" t="inlineStr">
         <is>
-          <t>grad*</t>
+          <t>grad</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
         <is>
-          <t>koordinate*</t>
+          <t>koordinate</t>
         </is>
       </c>
       <c r="F1" s="3" t="inlineStr">
         <is>
+          <t>pokriva_regije</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>pokrivanje_napomena</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="inlineStr">
+        <is>
           <t>nacin_cijene*</t>
         </is>
       </c>
-      <c r="G1" s="3" t="inlineStr">
+      <c r="I1" s="3" t="inlineStr">
         <is>
           <t>cijena_od*</t>
         </is>
       </c>
-      <c r="H1" s="3" t="inlineStr">
+      <c r="J1" s="3" t="inlineStr">
         <is>
           <t>cijena_do</t>
         </is>
       </c>
-      <c r="I1" s="3" t="inlineStr">
+      <c r="K1" s="3" t="inlineStr">
         <is>
           <t>ocjena</t>
         </is>
       </c>
-      <c r="J1" s="3" t="inlineStr">
+      <c r="L1" s="3" t="inlineStr">
         <is>
           <t>broj_recenzija</t>
         </is>
       </c>
-      <c r="K1" s="3" t="inlineStr">
+      <c r="M1" s="3" t="inlineStr">
         <is>
           <t>izvor_ocjene</t>
         </is>
       </c>
-      <c r="L1" s="3" t="inlineStr">
+      <c r="N1" s="3" t="inlineStr">
         <is>
           <t>provjereno</t>
         </is>
       </c>
-      <c r="M1" s="3" t="inlineStr">
+      <c r="O1" s="3" t="inlineStr">
         <is>
           <t>kalendar_uzivo</t>
         </is>
       </c>
-      <c r="N1" s="3" t="inlineStr">
+      <c r="P1" s="3" t="inlineStr">
         <is>
           <t>stil</t>
         </is>
       </c>
-      <c r="O1" s="3" t="inlineStr">
+      <c r="Q1" s="3" t="inlineStr">
         <is>
           <t>o_pruzatelju</t>
         </is>
       </c>
-      <c r="P1" s="3" t="inlineStr">
+      <c r="R1" s="3" t="inlineStr">
         <is>
           <t>usluge</t>
         </is>
       </c>
-      <c r="Q1" s="3" t="inlineStr">
+      <c r="S1" s="3" t="inlineStr">
+        <is>
+          <t>instagram</t>
+        </is>
+      </c>
+      <c r="T1" s="3" t="inlineStr">
+        <is>
+          <t>facebook</t>
+        </is>
+      </c>
+      <c r="U1" s="3" t="inlineStr">
         <is>
           <t>web</t>
         </is>
       </c>
-      <c r="R1" s="3" t="inlineStr">
+      <c r="V1" s="3" t="inlineStr">
         <is>
           <t>telefon</t>
         </is>
       </c>
-      <c r="S1" s="3" t="inlineStr">
+      <c r="W1" s="3" t="inlineStr">
         <is>
           <t>email</t>
         </is>
       </c>
-      <c r="T1" s="3" t="inlineStr">
+      <c r="X1" s="3" t="inlineStr">
         <is>
           <t>status</t>
         </is>
       </c>
-      <c r="U1" s="3" t="inlineStr">
+      <c r="Y1" s="3" t="inlineStr">
         <is>
           <t>napomena</t>
         </is>
@@ -1143,74 +1251,86 @@
           <t>43.5147, 16.4102</t>
         </is>
       </c>
-      <c r="F2" s="4" t="inlineStr">
+      <c r="F2" s="4" t="inlineStr"/>
+      <c r="G2" s="4" t="inlineStr"/>
+      <c r="H2" s="4" t="inlineStr">
         <is>
           <t>po osobi (raspon)</t>
         </is>
       </c>
-      <c r="G2" s="4" t="n">
+      <c r="I2" s="4" t="n">
         <v>65</v>
       </c>
-      <c r="H2" s="4" t="n">
+      <c r="J2" s="4" t="n">
         <v>95</v>
       </c>
-      <c r="I2" s="4" t="n">
+      <c r="K2" s="4" t="n">
         <v>4.8</v>
       </c>
-      <c r="J2" s="4" t="n">
+      <c r="L2" s="4" t="n">
         <v>57</v>
       </c>
-      <c r="K2" s="4" t="inlineStr">
+      <c r="M2" s="4" t="inlineStr">
         <is>
           <t>Google recenzije</t>
         </is>
       </c>
-      <c r="L2" s="4" t="inlineStr">
+      <c r="N2" s="4" t="inlineStr">
         <is>
           <t>DA</t>
         </is>
       </c>
-      <c r="M2" s="4" t="inlineStr">
+      <c r="O2" s="4" t="inlineStr">
         <is>
           <t>NE</t>
         </is>
       </c>
-      <c r="N2" s="4" t="inlineStr">
+      <c r="P2" s="4" t="inlineStr">
         <is>
           <t>uz more, terasa</t>
         </is>
       </c>
-      <c r="O2" s="4" t="inlineStr">
+      <c r="Q2" s="4" t="inlineStr">
         <is>
           <t>Terasa uz more za do 220 gostiju, vlastita kuhinja i parking. Cijena po osobi uključuje meni od 5 slijedova.</t>
         </is>
       </c>
-      <c r="P2" s="4" t="inlineStr">
+      <c r="R2" s="4" t="inlineStr">
         <is>
           <t>Meni po osobi, Osoblje, Osnovna dekoracija, Parking</t>
         </is>
       </c>
-      <c r="Q2" s="4" t="inlineStr">
+      <c r="S2" s="4" t="inlineStr">
+        <is>
+          <t>@villa.dalmacija</t>
+        </is>
+      </c>
+      <c r="T2" s="4" t="inlineStr">
+        <is>
+          <t>facebook.com/villadalmacija</t>
+        </is>
+      </c>
+      <c r="U2" s="4" t="inlineStr">
         <is>
           <t>villa-dalmacija.hr</t>
         </is>
       </c>
-      <c r="R2" s="4" t="inlineStr">
+      <c r="V2" s="4" t="inlineStr">
         <is>
           <t>021/555-123</t>
         </is>
       </c>
-      <c r="S2" s="4" t="inlineStr">
+      <c r="W2" s="4" t="inlineStr">
         <is>
           <t>info@villa-dalmacija.hr</t>
         </is>
       </c>
-      <c r="T2" s="4" t="inlineStr">
+      <c r="X2" s="4" t="inlineStr">
         <is>
           <t>Dozvola dobivena</t>
         </is>
       </c>
-      <c r="U2" s="4" t="inlineStr">
+      <c r="Y2" s="4" t="inlineStr">
         <is>
           <t>primjer — obriši ili ostavi (preskače se)</t>
         </is>
@@ -1244,60 +1364,315 @@
       </c>
       <c r="F3" s="4" t="inlineStr">
         <is>
+          <t>Dalmacija; Kvarner</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>radi u Splitu, Zadru i Šibeniku, po dogovoru i šire</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
           <t>od (paušal)</t>
         </is>
       </c>
-      <c r="G3" s="4" t="n">
+      <c r="I3" s="4" t="n">
         <v>850</v>
       </c>
-      <c r="H3" s="4" t="n"/>
-      <c r="I3" s="4" t="n">
+      <c r="J3" s="4" t="n"/>
+      <c r="K3" s="4" t="n">
         <v>4.8</v>
       </c>
-      <c r="J3" s="4" t="n">
+      <c r="L3" s="4" t="n">
         <v>31</v>
       </c>
-      <c r="K3" s="4" t="inlineStr">
+      <c r="M3" s="4" t="inlineStr">
         <is>
           <t>Google recenzije</t>
         </is>
       </c>
-      <c r="L3" s="4" t="inlineStr">
+      <c r="N3" s="4" t="inlineStr">
         <is>
           <t>DA</t>
         </is>
       </c>
-      <c r="M3" s="4" t="inlineStr">
+      <c r="O3" s="4" t="inlineStr">
         <is>
           <t>NE</t>
         </is>
       </c>
-      <c r="N3" s="4" t="inlineStr">
+      <c r="P3" s="4" t="inlineStr">
         <is>
           <t>boho, film</t>
         </is>
       </c>
-      <c r="O3" s="4" t="inlineStr">
+      <c r="Q3" s="4" t="inlineStr">
         <is>
           <t>Vjenčanja fotografiramo od 2014. — reportažno, s naglaskom na svjetlo i emociju.</t>
         </is>
       </c>
-      <c r="P3" s="4" t="inlineStr"/>
-      <c r="Q3" s="4" t="inlineStr">
+      <c r="R3" s="4" t="inlineStr"/>
+      <c r="S3" s="4" t="inlineStr">
+        <is>
+          <t>https://instagram.com/foto.anic</t>
+        </is>
+      </c>
+      <c r="T3" s="4" t="inlineStr"/>
+      <c r="U3" s="4" t="inlineStr">
         <is>
           <t>fotostudio-anic.hr</t>
         </is>
       </c>
-      <c r="R3" s="4" t="inlineStr"/>
-      <c r="S3" s="4" t="inlineStr"/>
-      <c r="T3" s="4" t="inlineStr">
+      <c r="V3" s="4" t="inlineStr"/>
+      <c r="W3" s="4" t="inlineStr"/>
+      <c r="X3" s="4" t="inlineStr">
         <is>
           <t>Kontaktirano</t>
         </is>
       </c>
-      <c r="U3" s="4" t="inlineStr">
+      <c r="Y3" s="4" t="inlineStr">
         <is>
           <t>primjer — preskače se pri importu</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>PRIMJER — Bend Adria</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>Glazba — bendovi</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>Dalmacija</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr"/>
+      <c r="E4" s="4" t="inlineStr"/>
+      <c r="F4" s="4" t="inlineStr"/>
+      <c r="G4" s="4" t="inlineStr"/>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>od (paušal)</t>
+        </is>
+      </c>
+      <c r="I4" s="4" t="n">
+        <v>1200</v>
+      </c>
+      <c r="J4" s="4" t="n"/>
+      <c r="K4" s="4" t="n"/>
+      <c r="L4" s="4" t="n"/>
+      <c r="M4" s="4" t="inlineStr"/>
+      <c r="N4" s="4" t="inlineStr">
+        <is>
+          <t>NE</t>
+        </is>
+      </c>
+      <c r="O4" s="4" t="inlineStr">
+        <is>
+          <t>NE</t>
+        </is>
+      </c>
+      <c r="P4" s="4" t="inlineStr">
+        <is>
+          <t>pop, rock</t>
+        </is>
+      </c>
+      <c r="Q4" s="4" t="inlineStr"/>
+      <c r="R4" s="4" t="inlineStr"/>
+      <c r="S4" s="4" t="inlineStr"/>
+      <c r="T4" s="4" t="inlineStr"/>
+      <c r="U4" s="4" t="inlineStr">
+        <is>
+          <t>bend-adria.hr</t>
+        </is>
+      </c>
+      <c r="V4" s="4" t="inlineStr"/>
+      <c r="W4" s="4" t="inlineStr"/>
+      <c r="X4" s="4" t="inlineStr">
+        <is>
+          <t>Istraženo</t>
+        </is>
+      </c>
+      <c r="Y4" s="4" t="inlineStr">
+        <is>
+          <t>primjer — bez grada/koordinata → bez pina</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>PRIMJER — Ana Fotografija</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>Foto i Video</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>Istra</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>Pula</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr"/>
+      <c r="F5" s="4" t="inlineStr"/>
+      <c r="G5" s="4" t="inlineStr"/>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>na upit</t>
+        </is>
+      </c>
+      <c r="I5" s="4" t="n"/>
+      <c r="J5" s="4" t="n"/>
+      <c r="K5" s="4" t="n"/>
+      <c r="L5" s="4" t="n"/>
+      <c r="M5" s="4" t="inlineStr"/>
+      <c r="N5" s="4" t="inlineStr">
+        <is>
+          <t>NE</t>
+        </is>
+      </c>
+      <c r="O5" s="4" t="inlineStr">
+        <is>
+          <t>NE</t>
+        </is>
+      </c>
+      <c r="P5" s="4" t="inlineStr">
+        <is>
+          <t>elegantno</t>
+        </is>
+      </c>
+      <c r="Q5" s="4" t="inlineStr"/>
+      <c r="R5" s="4" t="inlineStr"/>
+      <c r="S5" s="4" t="inlineStr"/>
+      <c r="T5" s="4" t="inlineStr"/>
+      <c r="U5" s="4" t="inlineStr"/>
+      <c r="V5" s="4" t="inlineStr"/>
+      <c r="W5" s="4" t="inlineStr"/>
+      <c r="X5" s="4" t="inlineStr">
+        <is>
+          <t>Istraženo</t>
+        </is>
+      </c>
+      <c r="Y5" s="4" t="inlineStr">
+        <is>
+          <t>primjer — koordinate se geokodiraju iz grada</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>PRIMJER — Perfect Day Weddings</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>Organizatori vjenčanja</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>Zagreb i okolica</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>Zagreb</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>45.8150, 15.9819</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>cijela Hrvatska</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>organiziramo vjenčanja u cijeloj Hrvatskoj</t>
+        </is>
+      </c>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>na upit</t>
+        </is>
+      </c>
+      <c r="I6" s="4" t="n"/>
+      <c r="J6" s="4" t="n"/>
+      <c r="K6" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="L6" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="M6" s="4" t="inlineStr">
+        <is>
+          <t>Google recenzije</t>
+        </is>
+      </c>
+      <c r="N6" s="4" t="inlineStr">
+        <is>
+          <t>DA</t>
+        </is>
+      </c>
+      <c r="O6" s="4" t="inlineStr">
+        <is>
+          <t>NE</t>
+        </is>
+      </c>
+      <c r="P6" s="4" t="inlineStr">
+        <is>
+          <t>full service</t>
+        </is>
+      </c>
+      <c r="Q6" s="4" t="inlineStr">
+        <is>
+          <t>Organiziramo vjenčanja od Istre do Slavonije — od koncepta do izvedbe.</t>
+        </is>
+      </c>
+      <c r="R6" s="4" t="inlineStr"/>
+      <c r="S6" s="4" t="inlineStr">
+        <is>
+          <t>@perfectday.hr</t>
+        </is>
+      </c>
+      <c r="T6" s="4" t="inlineStr">
+        <is>
+          <t>facebook.com/perfectdayweddings</t>
+        </is>
+      </c>
+      <c r="U6" s="4" t="inlineStr">
+        <is>
+          <t>perfectday.hr</t>
+        </is>
+      </c>
+      <c r="V6" s="4" t="inlineStr"/>
+      <c r="W6" s="4" t="inlineStr"/>
+      <c r="X6" s="4" t="inlineStr">
+        <is>
+          <t>Dozvola dobivena</t>
+        </is>
+      </c>
+      <c r="Y6" s="4" t="inlineStr">
+        <is>
+          <t>primjer — pokriva cijelu HR</t>
         </is>
       </c>
     </row>
@@ -1309,16 +1684,16 @@
     <dataValidation sqref="C2:C500" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>Sifrarnici!$B$1:$B$5</formula1>
     </dataValidation>
-    <dataValidation sqref="F2:F500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="H2:H500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"od (paušal),po osobi (raspon)"</formula1>
     </dataValidation>
-    <dataValidation sqref="L2:L500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="N2:N500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"DA,NE"</formula1>
     </dataValidation>
-    <dataValidation sqref="M2:M500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="O2:O500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"DA,NE"</formula1>
     </dataValidation>
-    <dataValidation sqref="T2:T500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="X2:X500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>Sifrarnici!$C$1:$C$4</formula1>
     </dataValidation>
   </dataValidations>

--- a/data/vendors-template.xlsx
+++ b/data/vendors-template.xlsx
@@ -630,7 +630,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A26"/>
+  <dimension ref="A1:A30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" min="1" max="1"/>
@@ -779,24 +779,48 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>• Redci čiji naziv počinje s 'PRIMJER' se preskaču pri importu — slobodno ih ostavi ili obriši.</t>
-        </is>
-      </c>
+      <c r="A23" s="2" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="inlineStr"/>
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t>INTERNI STATUSI (nikad javne negativne oznake):</t>
+        </is>
+      </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="inlineStr">
-        <is>
-          <t>SAVJET ZA POČETAK:</t>
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>• Sumnjaš da je pružatelj neaktivan, prijavljen je problem ili podaci ne valjaju? Status = Skriveno → import ga preskače (tiho uklanjanje s platforme).</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>• Detalje sumnje zapiši u kolonu napomena. Kad provjeriš i potvrdiš da je sve u redu, vrati status i pružatelj se opet uvozi.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>• Redci čiji naziv počinje s 'PRIMJER' se preskaču pri importu — slobodno ih ostavi ili obriši.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="inlineStr">
+        <is>
+          <t>SAVJET ZA POČETAK:</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
         <is>
           <t>• Kreni s 1 regijom i 2–3 kategorije (npr. Dalmacija: Restorani i sale + Foto i Video) da provjeriš cijeli tok, pa širi.</t>
         </is>
@@ -893,6 +917,11 @@
       <c r="B5" t="inlineStr">
         <is>
           <t>Slavonija</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Skriveno</t>
         </is>
       </c>
     </row>
@@ -1694,7 +1723,7 @@
       <formula1>"DA,NE"</formula1>
     </dataValidation>
     <dataValidation sqref="X2:X500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>Sifrarnici!$C$1:$C$4</formula1>
+      <formula1>Sifrarnici!$C$1:$C$5</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
